--- a/Result/profitability/7822.xlsx
+++ b/Result/profitability/7822.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM9"/>
+  <dimension ref="A1:AM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1118,7 +1118,7 @@
         <v>112</v>
       </c>
       <c r="L6" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1147,10 +1147,10 @@
         <v>114.2</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1700000000000004</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="X6" t="n">
-        <v>0.06719367588932812</v>
+        <v>0.06324110671936767</v>
       </c>
       <c r="Y6" t="n">
         <v>1.369999999999997</v>
@@ -1159,10 +1159,10 @@
         <v>0.02274236387782191</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="AB6" t="n">
-        <v>-3.783505154639176</v>
+        <v>-3.77319587628866</v>
       </c>
       <c r="AC6" t="n">
         <v>5.269999999999996</v>
@@ -1270,10 +1270,10 @@
         <v>114.3</v>
       </c>
       <c r="W7" t="n">
-        <v>0.9099999999999997</v>
+        <v>0.9199999999999999</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3370370370370368</v>
+        <v>0.3420074349442379</v>
       </c>
       <c r="Y7" t="n">
         <v>1.630000000000003</v>
@@ -1490,7 +1490,7 @@
         <v>4.93</v>
       </c>
       <c r="M9" t="n">
-        <v>2.84625</v>
+        <v>2.845</v>
       </c>
       <c r="N9" t="n">
         <v>60.1075</v>
@@ -1571,6 +1571,133 @@
       </c>
       <c r="AM9" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>7822</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>735</v>
+      </c>
+      <c r="D10" t="n">
+        <v>297</v>
+      </c>
+      <c r="E10" t="n">
+        <v>438</v>
+      </c>
+      <c r="F10" t="n">
+        <v>59.64</v>
+      </c>
+      <c r="G10" t="n">
+        <v>275</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>37.48%</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>22</v>
+      </c>
+      <c r="J10" t="n">
+        <v>297</v>
+      </c>
+      <c r="K10" t="n">
+        <v>236</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.615</v>
+      </c>
+      <c r="N10" t="n">
+        <v>60.52</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.2600000000000007</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.05273833671399619</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.4699999999999989</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.007943214466790582</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9293680297397771</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-1.969999999999999</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-0.03197532868040898</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK10" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
